--- a/data/fixture_rich_v2.xlsx
+++ b/data/fixture_rich_v2.xlsx
@@ -1487,7 +1487,7 @@
         <v>2</v>
       </c>
       <c r="S13" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="str">
         <v>1600</v>

--- a/data/fixture_rich_v2.xlsx
+++ b/data/fixture_rich_v2.xlsx
@@ -1487,7 +1487,7 @@
         <v>2</v>
       </c>
       <c r="S13" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="str">
         <v>1600</v>
